--- a/public/business-plans/construction.xlsx
+++ b/public/business-plans/construction.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,10 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
@@ -66,12 +70,17 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,19 +133,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -558,10 +570,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Строительство». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
+          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Строительство». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Абзацы, отмеченные как «ПРИМЕР», — иллюстрация формата ответа, а не факты о реальной компании; замените их своими данными. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
         </is>
       </c>
     </row>
@@ -579,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -592,31 +604,39 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): ООО «UsSaz Qurilish» специализируется на комплексном ремонте квартир и коммерческих помещений в Ташкенте «под ключ» — от дизайн-проекта до сдачи объекта. Требуемые инвестиции — 400 млн сум на инструмент, спецтехнику и оборотный капитал на первые 3 объекта; окупаемость — около 14 месяцев при загрузке 2-3 объекта одновременно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] В 5-8 предложениях: суть проекта, какую проблему решает, для кого, требуемая сумма инвестиций и на что она пойдёт, ожидаемый результат (выручка/прибыль/срок окупаемости).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Описание компании / проекта</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Организационно-правовая форма (ИП/ООО/фермерское хозяйство), команда, текущий статус проекта (идея / MVP / действующий бизнес), уникальное торговое предложение.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -628,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -641,68 +661,84 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="44" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>•  Строительство — один из ключевых драйверов ВВП Узбекистана на фоне активных жилищных и инфраструктурных программ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
+          <t>•  Строительство — один из ключевых драйверов роста экономики Узбекистана на фоне активных жилищных и инфраструктурных программ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="89" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>•  Действуют ипотечные программы и программы реновации городской среды, поддерживающие спрос на строительные и ремонтные услуги.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>•  Указом от 20 ноября 2025 года утверждена национальная программа развития жилищного строительства и ипотеки до 2040 года: ежегодный ввод жилья планируется удвоить до 421 тыс. объектов, ипотечный портфель — вырастить более чем в 10 раз (до $56,7 млрд), а долю современного жилья в жилом фонде — довести до 50% (gazeta.uz). Это создаёт долгосрочный спрос на строительные и ремонтные услуги, но конкретные региональные квоты и условия стоит уточнять по мере запуска программы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="59" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>•  Растёт спрос на энергоэффективные и сейсмостойкие решения — соответствие актуальным строительным нормам (KMK) важно для конкурентоспособности.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>•  Параллельно продолжаются программы реновации городской среды и инфраструктурные проекты (дороги, объекты соцкультбыта) — поддерживают спрос на подрядные и субподрядные работы для среднего и малого бизнеса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="74" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>•  [Впишите] Объём рынка и конкурентов в вашем сегменте (жилое/коммерческое/промышленное строительство) и регионе.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Конкуренты</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
+          <t>•  Растёт спрос на энергоэффективные и сейсмостойкие решения — новая жилищная программа прямо предусматривает экологичные материалы и энергоэффективные технологии; соответствие актуальным строительным нормам (KMK) и этим требованиям важно для конкурентоспособности при госзаказах и в ипотечных проектах.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="74" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>•  Для сравнения: в Казахстане и России также действуют масштабные программы льготной ипотеки — конкуренция за импортное оборудование, отделочные материалы и подрядчиков с международным опытом в регионе в целом растёт, что может повышать закупочные цены на отдельные материалы и технику.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="59" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>•  [Впишите] Объём рынка и конкурентов в вашем сегменте (жилое/коммерческое/промышленное/инфраструктурное строительство) и регионе — уточняйте по данным местного хокимията и тендерным площадкам.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Целевая аудитория</t>
+          <t>Конкуренты</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Целевая аудитория</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>[Впишите] Портрет основного клиента: кто он, что для него важно при выборе, где его найти.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A10:D10"/>
   </mergeCells>
@@ -716,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -729,117 +765,183 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цена — по смете с фиксацией на этапе договора, чтобы избежать споров при росте цен на материалы; продвижение — портфолио отремонтированных объектов в соцсетях и на агрегаторах ремонта, сарафанное радио через застройщиков и риелторов, первые 2-3 объекта — по льготной цене за отзывы и портфолио.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Ценообразование, каналы продвижения и продаж, план привлечения первых клиентов.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Операционный план</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="74" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цикл: замер и смета → согласование дизайн-проекта → закупка материалов → черновые и чистовые работы бригадой → сдача объекта заказчику. Ключевые поставщики материалов — 2-3 оптовые базы стройматериалов с отсрочкой платежа. Требуется лицензирование строительной деятельности.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Процесс производства/оказания услуги, ключевые поставщики, оборудование, необходимые лицензии и разрешения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Организационный план</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>Организационный план</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Директор-прораб, 2 бригады по 4-5 человек (штукатуры-маляры, электрики, сантехники), сметчик на аутсорсе, менеджер по работе с клиентами. Форма — ООО с упрощённым налоговым режимом на старте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Риски и меры по их снижению (примеры для отрасли)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Меры снижения</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Рост цен на стройматериалы</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Фиксация цен/предоплата у ключевых поставщиков</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="13" ht="59" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Рост цен на стройматериалы в ходе исполнения долгосрочных договоров</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Фиксация цен/предоплата у ключевых поставщиков, пункт о пересмотре сметы при росте цен свыше порога</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Задержки оплат заказчиками</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Поэтапная оплата по договору, авансирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Сезонность спроса</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Диверсификация видов работ (внутренняя отделка зимой)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Поэтапная оплата по договору, авансирование, штрафные санкции за просрочку в договоре</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="59" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Сезонность спроса (замедление в холодные месяцы)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Диверсификация видов работ (внутренняя отделка зимой, наружные и кровельные — в тёплый сезон)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Дефицит квалифицированных рабочих (каменщики, сварщики, отделочники)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Долгосрочные отношения с проверенными бригадами, обучение подмастерьев</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Изменение строительных норм (KMK) и требований по энергоэффективности</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Регулярный мониторинг нормативной базы, повышение квалификации ИТР</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Срыв сроков субподрядчиками</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Резервные подрядчики на критичные виды работ, штрафные условия в договорах субподряда</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Дополните таблицу своими рисками, специфичными для вашего проекта и региона.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="21">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -851,328 +953,361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Сумма, сум</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Добавляйте свои строки при необходимости.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Регистрация и лицензирование строительной деятельности</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Инструменты и спецтехника</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="B8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>аренда или покупка</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Первоначальный запас материалов</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="B9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Офис / склад</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="B10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Страхование ответственности</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="B11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="21" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
+          <t>Спецодежда и средства индивидуальной защиты для бригад</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
           <t>Итого: стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B12" s="15">
-        <f>SUM(B7:B11)</f>
+      <c r="B13" s="16">
+        <f>SUM(B7:B12)</f>
         <v/>
       </c>
-      <c r="C12" s="16" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="C13" s="17" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Подрядные договоры на объекты</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Ремонтно-отделочные работы</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="B17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Проектирование и сметы</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="B18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Гарантийное и постгарантийное обслуживание объектов</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B18" s="15">
-        <f>SUM(B15:B17)</f>
+      <c r="B20" s="16">
+        <f>SUM(B16:B19)</f>
         <v/>
       </c>
-      <c r="C18" s="16" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="C20" s="17" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>ФОТ бригад</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="B23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Материалы</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Аренда техники</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="B25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Субподряд</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Транспорт и логистика</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="B27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Страхование объектов и ответственности</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="B29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B27" s="15">
-        <f>SUM(B21:B26)</f>
+      <c r="B30" s="16">
+        <f>SUM(B23:B29)</f>
         <v/>
       </c>
-      <c r="C27" s="16" t="n"/>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="C30" s="17" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Ежемесячная прибыль</t>
         </is>
       </c>
-      <c r="B29" s="10">
-        <f>B18-B27</f>
+      <c r="B32" s="11">
+        <f>B20-B30</f>
         <v/>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Срок выхода на окупаемость, мес.</t>
         </is>
       </c>
-      <c r="B31" s="13">
-        <f>IFERROR(B4/B29,"—")</f>
+      <c r="B34" s="14">
+        <f>IFERROR(B4/B32,"—")</f>
         <v/>
       </c>
-      <c r="C31" s="13">
+      <c r="C34" s="14">
         <f> Начальные инвестиции / Ежемесячная прибыль</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Рентабельность продаж, %</t>
         </is>
       </c>
-      <c r="B32" s="17">
-        <f>IFERROR(B29/B18*100,"—")</f>
+      <c r="B35" s="18">
+        <f>IFERROR(B32/B20*100,"—")</f>
         <v/>
       </c>
-      <c r="C32" s="13">
+      <c r="C35" s="14">
         <f> Ежемесячная прибыль / Выручка × 100%</f>
         <v/>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта.</t>
+    <row r="36"/>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A37:C37"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/business-plans/construction.xlsx
+++ b/public/business-plans/construction.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +126,9 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -498,14 +505,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ФИНАНСОВЫЙ ПЛАН: СТРОИТЕЛЬСТВО</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>ФИНАНСОВЫЙ ПЛАН: СТРОИТЕЛЬСТВО — ПРИМЕР РАСЧЁТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Строительство» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — только расчётная часть с рабочими формулами.</t>
+          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Строительство» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — расчётная часть с рабочими формулами, уже заполненная цифрами ПРИМЕРА (иллюстративная компания из резюме бизнес-плана, не реальный заёмщик) — чтобы показать порядок величины и логику расчёта. Перед подачей в банк или инвестору замените суммы на данные своего проекта.</t>
         </is>
       </c>
     </row>
@@ -527,10 +534,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
+          <t>Столбец «Сумма, сум» уже заполнен примером расчёта для иллюстративной компании из этого бизнес-плана — на основе рыночных ориентиров 2025-2026 года (там, где источник известен — со ссылкой в комментарии) или экспертной оценки порядка величины (это тоже отмечено). Итоги, прибыль, срок окупаемости и рентабельность ниже пересчитаются автоматически (это формулы). Замените суммы в столбце B на данные вашего собственного проекта — тогда пересчитается всё.</t>
         </is>
       </c>
     </row>
@@ -541,8 +548,9 @@
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
+      <c r="B7" s="6">
+        <f>B16</f>
+        <v/>
       </c>
     </row>
     <row r="8"/>
@@ -555,75 +563,95 @@
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
     </row>
-    <row r="10" ht="21" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Регистрация и лицензирование строительной деятельности</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11" ht="21" customHeight="1">
+        <v>18000000</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: регистрация ООО, строительная лицензия (квалификация кадров, техническая экспертиза)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Инструменты и спецтехника</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
+        <v>138000000</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>аренда или покупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
+          <t>аренда или покупка — Пример: оценка: комплект инструмента для 2 бригад, леса/вышка-тура, бетономешалка, генератор, компрессор, б/у грузовик</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Первоначальный запас материалов</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
+        <v>150000000</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: складской запас отделочных материалов (~1 мес.) для старта первых 2-3 объектов до авансов заказчиков</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Офис / склад</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr"/>
-    </row>
-    <row r="14" ht="21" customHeight="1">
+        <v>70000000</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: депозит + ремонт офисно-складского помещения; офисы класса B/B+ в Ташкенте — ~$26,4/м²/мес (CMWP/spot.uz, окт. 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Страхование ответственности</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+        <v>15000000</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка первой годовой премии страхования гражданской ответственности подрядчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Спецодежда и средства индивидуальной защиты для бригад</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr"/>
+        <v>9000000</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: комплекты СИЗ на ~10 человек (2 бригады по 4-5 чел.)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -647,49 +675,65 @@
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
     </row>
-    <row r="19" ht="21" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Подрядные договоры на объекты</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20" ht="21" customHeight="1">
+        <v>170000000</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 50% от выручки — крупные проекты «под ключ» при загрузке 2-3 объекта одновременно</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Ремонтно-отделочные работы</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21" ht="21" customHeight="1">
+        <v>102000000</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 30% от выручки — более мелкие частные заказы на отделку</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Проектирование и сметы</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr"/>
-    </row>
-    <row r="22" ht="21" customHeight="1">
+        <v>34000000</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 10% от выручки — сопутствующая услуга проектирования/смет</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Гарантийное и постгарантийное обслуживание объектов</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="9" t="inlineStr"/>
+        <v>34000000</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 10% от выручки — сервисное обслуживание ранее сданных объектов</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -713,60 +757,80 @@
       <c r="B25" s="8" t="n"/>
       <c r="C25" s="8" t="n"/>
     </row>
-    <row r="26" ht="21" customHeight="1">
+    <row r="26" ht="51" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>ФОТ бригад</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
+        <v>84000000</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 2 бригады по 4-5 чел. + директор-прораб, сметчик, снабженец, бухгалтер на аутсорсе — оценка зарплат отделочников в Ташкенте</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Материалы</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
+        <v>153000000</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Пример: ~45% от выручки — типовая доля материалов в стоимости ремонта «под ключ»</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Аренда техники</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29" ht="21" customHeight="1">
+        <v>8000000</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка аренды спецтехники (подъёмники, генераторы) на объектах</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Субподряд</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
+        <v>34000000</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Пример: ~10% от выручки — узкоспециализированные субподрядчики (электрика, кондиционирование)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Транспорт и логистика</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr"/>
+        <v>6000000</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка доставки материалов и перемещения бригад между объектами</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
@@ -775,20 +839,28 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32" ht="21" customHeight="1">
+        <v>3000000</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка ежемесячной части страховой премии</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="9" t="inlineStr"/>
+        <v>23700000</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Пример: соц. налог 12% от ФОТ (2026 г.) + оценка налога с оборота/на прибыль ~4% от выручки</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
@@ -825,9 +897,10 @@
         <f>IFERROR(B7/B35,"—")</f>
         <v/>
       </c>
-      <c r="C37" s="9">
-        <f> Начальные инвестиции / Ежемесячная прибыль</f>
-        <v/>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Начальные инвестиции ÷ Ежемесячная прибыль</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -840,22 +913,32 @@
         <f>IFERROR(B35/B23*100,"—")</f>
         <v/>
       </c>
-      <c r="C38" s="9">
-        <f> Ежемесячная прибыль / Выручка × 100%</f>
-        <v/>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Ежемесячная прибыль ÷ Выручка × 100%</t>
+        </is>
       </c>
     </row>
     <row r="39"/>
-    <row r="40" ht="40" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
+    <row r="40" ht="50" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Как считался этот пример: Сумма стартовых затрат — ровно 400 млн сум, полностью соответствует резюме. Прибыль ≈28,3 млн сум/мес при выручке 340 млн/мес даёт окупаемость ≈14,1 мес. — соответствует резюме.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42" ht="55" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Это пример расчёта для иллюстративной компании, а не готовая заявка на кредит и не проверенные рыночные данные о реальном бизнесе. Суммы в столбце B — рабочие формулы: замените их на цифры вашего проекта, и итоги, прибыль, срок окупаемости и рентабельность пересчитаются автоматически. Там, где в комментарии указан источник — это ориентир на 2025-2026 год, проверяйте актуальность перед подачей документов в банк; где указана «экспертная оценка» — это иллюстрация порядка величины, а не факт.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A40:C40"/>
   </mergeCells>
